--- a/output/Data and Chart Outputs/china_ndrc_gas_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_ndrc_gas_monthly.xlsx
@@ -194,12 +194,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$28</f>
+              <f>'Chart'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$28</f>
+              <f>'Chart'!$B$2:$B$35</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -330,12 +330,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - natural gas apparent 1'!$A$2:$A$28</f>
+              <f>'Chart - natural gas apparent 1'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - natural gas apparent 1'!$B$2:$B$28</f>
+              <f>'Chart - natural gas apparent 1'!$B$2:$B$35</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -829,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -857,209 +857,265 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>45078</v>
+        <v>45047</v>
       </c>
       <c r="B3" t="n">
-        <v>32.52</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>45108</v>
+        <v>45078</v>
       </c>
       <c r="B4" t="n">
-        <v>32.49</v>
+        <v>32.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>45139</v>
+        <v>45108</v>
       </c>
       <c r="B5" t="n">
-        <v>32.68</v>
+        <v>32.49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>45170</v>
+        <v>45139</v>
       </c>
       <c r="B6" t="n">
-        <v>29.61</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>45200</v>
+        <v>45170</v>
       </c>
       <c r="B7" t="n">
-        <v>31.92</v>
+        <v>29.61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>45231</v>
+        <v>45200</v>
       </c>
       <c r="B8" t="n">
-        <v>34.98</v>
+        <v>31.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>45261</v>
+        <v>45231</v>
       </c>
       <c r="B9" t="n">
-        <v>37.65</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>45474</v>
+        <v>45261</v>
       </c>
       <c r="B10" t="n">
-        <v>35.15</v>
+        <v>37.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>45505</v>
+        <v>45352</v>
       </c>
       <c r="B11" t="n">
-        <v>35.52</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>45536</v>
+        <v>45383</v>
       </c>
       <c r="B12" t="n">
-        <v>33.88</v>
+        <v>35.46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>45597</v>
+        <v>45413</v>
       </c>
       <c r="B13" t="n">
-        <v>34.86</v>
+        <v>35.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>45717</v>
+        <v>45444</v>
       </c>
       <c r="B14" t="n">
-        <v>35.79</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>45748</v>
+        <v>45474</v>
       </c>
       <c r="B15" t="n">
-        <v>34.73</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>45778</v>
+        <v>45505</v>
       </c>
       <c r="B16" t="n">
-        <v>36.42</v>
+        <v>35.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>45809</v>
+        <v>45536</v>
       </c>
       <c r="B17" t="n">
-        <v>35.05</v>
+        <v>33.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>45839</v>
+        <v>45566</v>
       </c>
       <c r="B18" t="n">
-        <v>36.17</v>
+        <v>35.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>45870</v>
+        <v>45597</v>
       </c>
       <c r="B19" t="n">
-        <v>36.41</v>
+        <v>34.86</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>45901</v>
+        <v>45627</v>
       </c>
       <c r="B20" t="n">
-        <v>33.19</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>45931</v>
+        <v>45717</v>
       </c>
       <c r="B21" t="n">
-        <v>34.77</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>45962</v>
+        <v>45748</v>
       </c>
       <c r="B22" t="n">
-        <v>36.28</v>
+        <v>34.73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>45992</v>
+        <v>45778</v>
       </c>
       <c r="B23" t="n">
-        <v>38.57</v>
+        <v>36.42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46082</v>
+        <v>45809</v>
       </c>
       <c r="B24" t="n">
-        <v>34.08</v>
+        <v>35.05</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46113</v>
+        <v>45839</v>
       </c>
       <c r="B25" t="n">
-        <v>33.69</v>
+        <v>36.17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46143</v>
+        <v>45870</v>
       </c>
       <c r="B26" t="n">
-        <v>34.98</v>
+        <v>36.41</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46174</v>
+        <v>45901</v>
       </c>
       <c r="B27" t="n">
-        <v>34.66</v>
+        <v>33.19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B28" t="n">
+        <v>34.77</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B29" t="n">
+        <v>36.28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B30" t="n">
+        <v>38.57</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B31" t="n">
+        <v>34.08</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B32" t="n">
+        <v>33.69</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B33" t="n">
+        <v>34.98</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B34" t="n">
+        <v>34.66</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
         <v>46204</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B35" t="n">
         <v>35.34</v>
       </c>
     </row>
@@ -1075,7 +1131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1103,209 +1159,265 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>45078</v>
+        <v>45047</v>
       </c>
       <c r="B3" t="n">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>45108</v>
+        <v>45078</v>
       </c>
       <c r="B4" t="n">
-        <v>9.6</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>45139</v>
+        <v>45108</v>
       </c>
       <c r="B5" t="n">
-        <v>11.1</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>45170</v>
+        <v>45139</v>
       </c>
       <c r="B6" t="n">
-        <v>5.8</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>45200</v>
+        <v>45170</v>
       </c>
       <c r="B7" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>45231</v>
+        <v>45200</v>
       </c>
       <c r="B8" t="n">
-        <v>9.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>45261</v>
+        <v>45231</v>
       </c>
       <c r="B9" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>45474</v>
+        <v>45261</v>
       </c>
       <c r="B10" t="n">
-        <v>7.7</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>45505</v>
+        <v>45352</v>
       </c>
       <c r="B11" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>45536</v>
+        <v>45383</v>
       </c>
       <c r="B12" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>45597</v>
+        <v>45413</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>45717</v>
+        <v>45444</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>45748</v>
+        <v>45474</v>
       </c>
       <c r="B15" t="n">
-        <v>-2</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>45778</v>
+        <v>45505</v>
       </c>
       <c r="B16" t="n">
-        <v>2.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>45809</v>
+        <v>45536</v>
       </c>
       <c r="B17" t="n">
-        <v>1.4</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>45839</v>
+        <v>45566</v>
       </c>
       <c r="B18" t="n">
-        <v>2.9</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>45870</v>
+        <v>45597</v>
       </c>
       <c r="B19" t="n">
-        <v>1.8</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>45901</v>
+        <v>45627</v>
       </c>
       <c r="B20" t="n">
-        <v>-1.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>45931</v>
+        <v>45717</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>45962</v>
+        <v>45748</v>
       </c>
       <c r="B22" t="n">
-        <v>5.1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>45992</v>
+        <v>45778</v>
       </c>
       <c r="B23" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46082</v>
+        <v>45809</v>
       </c>
       <c r="B24" t="n">
-        <v>-4.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46113</v>
+        <v>45839</v>
       </c>
       <c r="B25" t="n">
-        <v>-3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46143</v>
+        <v>45870</v>
       </c>
       <c r="B26" t="n">
-        <v>-4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46174</v>
+        <v>45901</v>
       </c>
       <c r="B27" t="n">
-        <v>-1.1</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B28" t="n">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B31" t="n">
+        <v>-4.8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B32" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B33" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B34" t="n">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
         <v>46204</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B35" t="n">
         <v>-2.6</v>
       </c>
     </row>
@@ -1321,7 +1433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1370,443 +1482,562 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>45078</v>
+        <v>45047</v>
       </c>
       <c r="B3" t="n">
-        <v>32.52</v>
+        <v>33.44</v>
       </c>
       <c r="C3" t="n">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
       <c r="D3" t="n">
-        <v>194.88</v>
+        <v>162.7</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>45108</v>
+        <v>45078</v>
       </c>
       <c r="B4" t="n">
-        <v>32.49</v>
+        <v>32.52</v>
       </c>
       <c r="C4" t="n">
-        <v>9.6</v>
+        <v>13.1</v>
       </c>
       <c r="D4" t="n">
-        <v>227.12</v>
+        <v>194.88</v>
       </c>
       <c r="E4" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>45139</v>
+        <v>45108</v>
       </c>
       <c r="B5" t="n">
-        <v>32.68</v>
+        <v>32.49</v>
       </c>
       <c r="C5" t="n">
-        <v>11.1</v>
+        <v>9.6</v>
       </c>
       <c r="D5" t="n">
-        <v>259.81</v>
+        <v>227.12</v>
       </c>
       <c r="E5" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>45170</v>
+        <v>45139</v>
       </c>
       <c r="B6" t="n">
-        <v>29.61</v>
+        <v>32.68</v>
       </c>
       <c r="C6" t="n">
-        <v>5.8</v>
+        <v>11.1</v>
       </c>
       <c r="D6" t="n">
-        <v>288.75</v>
+        <v>259.81</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>45200</v>
+        <v>45170</v>
       </c>
       <c r="B7" t="n">
-        <v>31.92</v>
+        <v>29.61</v>
       </c>
       <c r="C7" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="D7" t="n">
-        <v>321.71</v>
+        <v>288.75</v>
       </c>
       <c r="E7" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>45231</v>
+        <v>45200</v>
       </c>
       <c r="B8" t="n">
-        <v>34.98</v>
+        <v>31.92</v>
       </c>
       <c r="C8" t="n">
-        <v>9.4</v>
+        <v>4.5</v>
       </c>
       <c r="D8" t="n">
-        <v>356.61</v>
+        <v>321.71</v>
       </c>
       <c r="E8" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>45261</v>
+        <v>45231</v>
       </c>
       <c r="B9" t="n">
-        <v>37.65</v>
+        <v>34.98</v>
       </c>
       <c r="C9" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="D9" t="n">
-        <v>394.53</v>
+        <v>356.61</v>
       </c>
       <c r="E9" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>45474</v>
+        <v>45261</v>
       </c>
       <c r="B10" t="n">
-        <v>35.15</v>
+        <v>37.65</v>
       </c>
       <c r="C10" t="n">
-        <v>7.7</v>
+        <v>9.5</v>
       </c>
       <c r="D10" t="n">
-        <v>248.96</v>
+        <v>394.53</v>
       </c>
       <c r="E10" t="n">
-        <v>9.699999999999999</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>45505</v>
+        <v>45352</v>
       </c>
       <c r="B11" t="n">
-        <v>35.52</v>
+        <v>35.75</v>
       </c>
       <c r="C11" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="D11" t="n">
-        <v>284.48</v>
+        <v>108.26</v>
       </c>
       <c r="E11" t="n">
-        <v>9.6</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>45536</v>
+        <v>45383</v>
       </c>
       <c r="B12" t="n">
-        <v>33.88</v>
+        <v>35.46</v>
       </c>
       <c r="C12" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="D12" t="n">
-        <v>318.37</v>
+        <v>143.73</v>
       </c>
       <c r="E12" t="n">
-        <v>9.9</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>45597</v>
+        <v>45413</v>
       </c>
       <c r="B13" t="n">
-        <v>34.86</v>
+        <v>35.58</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.5</v>
+        <v>6.8</v>
       </c>
       <c r="D13" t="n">
-        <v>388.57</v>
+        <v>179.31</v>
       </c>
       <c r="E13" t="n">
-        <v>8.9</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>45717</v>
+        <v>45444</v>
       </c>
       <c r="B14" t="n">
-        <v>35.79</v>
+        <v>34.4</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1</v>
+        <v>6.9</v>
       </c>
       <c r="D14" t="n">
-        <v>105.75</v>
+        <v>213.75</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.2</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>45748</v>
+        <v>45474</v>
       </c>
       <c r="B15" t="n">
-        <v>34.73</v>
+        <v>35.15</v>
       </c>
       <c r="C15" t="n">
-        <v>-2</v>
+        <v>7.7</v>
       </c>
       <c r="D15" t="n">
-        <v>140.46</v>
+        <v>248.96</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.2</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>45778</v>
+        <v>45505</v>
       </c>
       <c r="B16" t="n">
-        <v>36.42</v>
+        <v>35.52</v>
       </c>
       <c r="C16" t="n">
-        <v>2.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>176.89</v>
+        <v>284.48</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.3</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>45809</v>
+        <v>45536</v>
       </c>
       <c r="B17" t="n">
-        <v>35.05</v>
+        <v>33.88</v>
       </c>
       <c r="C17" t="n">
-        <v>1.4</v>
+        <v>12.8</v>
       </c>
       <c r="D17" t="n">
-        <v>211.97</v>
+        <v>318.37</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>45839</v>
+        <v>45566</v>
       </c>
       <c r="B18" t="n">
-        <v>36.17</v>
+        <v>35.34</v>
       </c>
       <c r="C18" t="n">
-        <v>2.9</v>
+        <v>10.9</v>
       </c>
       <c r="D18" t="n">
-        <v>248.15</v>
+        <v>353.72</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>45870</v>
+        <v>45597</v>
       </c>
       <c r="B19" t="n">
-        <v>36.41</v>
+        <v>34.86</v>
       </c>
       <c r="C19" t="n">
-        <v>1.8</v>
+        <v>-0.5</v>
       </c>
       <c r="D19" t="n">
-        <v>284.56</v>
+        <v>388.57</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>45901</v>
+        <v>45627</v>
       </c>
       <c r="B20" t="n">
-        <v>33.19</v>
+        <v>37.84</v>
       </c>
       <c r="C20" t="n">
-        <v>-1.6</v>
+        <v>0.5</v>
       </c>
       <c r="D20" t="n">
-        <v>317.75</v>
+        <v>426.05</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>45931</v>
+        <v>45717</v>
       </c>
       <c r="B21" t="n">
-        <v>34.77</v>
+        <v>35.79</v>
       </c>
       <c r="C21" t="n">
-        <v>-1.3</v>
+        <v>0.1</v>
       </c>
       <c r="D21" t="n">
-        <v>352.53</v>
+        <v>105.75</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>45962</v>
+        <v>45748</v>
       </c>
       <c r="B22" t="n">
-        <v>36.28</v>
+        <v>34.73</v>
       </c>
       <c r="C22" t="n">
-        <v>5.1</v>
+        <v>-2</v>
       </c>
       <c r="D22" t="n">
-        <v>388</v>
+        <v>140.46</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>45992</v>
+        <v>45778</v>
       </c>
       <c r="B23" t="n">
-        <v>38.57</v>
+        <v>36.42</v>
       </c>
       <c r="C23" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="D23" t="n">
-        <v>426.55</v>
+        <v>176.89</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46082</v>
+        <v>45809</v>
       </c>
       <c r="B24" t="n">
-        <v>34.08</v>
+        <v>35.05</v>
       </c>
       <c r="C24" t="n">
-        <v>-4.8</v>
+        <v>1.4</v>
       </c>
       <c r="D24" t="n">
-        <v>103.4</v>
+        <v>211.97</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46113</v>
+        <v>45839</v>
       </c>
       <c r="B25" t="n">
-        <v>33.69</v>
+        <v>36.17</v>
       </c>
       <c r="C25" t="n">
-        <v>-3</v>
+        <v>2.9</v>
       </c>
       <c r="D25" t="n">
-        <v>137.2</v>
+        <v>248.15</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46143</v>
+        <v>45870</v>
       </c>
       <c r="B26" t="n">
-        <v>34.98</v>
+        <v>36.41</v>
       </c>
       <c r="C26" t="n">
-        <v>-4</v>
+        <v>1.8</v>
       </c>
       <c r="D26" t="n">
-        <v>172.18</v>
+        <v>284.56</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.7</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46174</v>
+        <v>45901</v>
       </c>
       <c r="B27" t="n">
-        <v>34.66</v>
+        <v>33.19</v>
       </c>
       <c r="C27" t="n">
-        <v>-1.1</v>
+        <v>-1.6</v>
       </c>
       <c r="D27" t="n">
-        <v>206.85</v>
+        <v>317.75</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.4</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B28" t="n">
+        <v>34.77</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>352.53</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B29" t="n">
+        <v>36.28</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>388</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B30" t="n">
+        <v>38.57</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D30" t="n">
+        <v>426.55</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B31" t="n">
+        <v>34.08</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B32" t="n">
+        <v>33.69</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>137.2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B33" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>172.18</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B34" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>206.85</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
         <v>46204</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B35" t="n">
         <v>35.34</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C35" t="n">
         <v>-2.6</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D35" t="n">
         <v>242.19</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E35" t="n">
         <v>-2.4</v>
       </c>
     </row>
@@ -1821,7 +2052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1853,12 +2084,34 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B2" t="n">
+        <v>72.51000000000001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B3" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
         <v>46054</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B4" t="n">
         <v>69.34999999999999</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C4" t="n">
         <v>-0.9</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/china_ndrc_gas_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_ndrc_gas_monthly.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Chart - natural gas apparent 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Chart - gas consumption y-y" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Data" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Jan-Feb" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Series" sheetId="6" state="visible" r:id="rId6"/>
@@ -158,7 +158,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>China natural gas apparent consumption (NDRC) (to Jul/26)</a:t>
+              <a:t>China gas apparent consumption (NDRC) (to Jul/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -294,7 +294,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>China natural gas apparent consumption y/y (NDRC) (to Jul/26)</a:t>
+              <a:t>China gas consumption y/y (NDRC) (to Jul/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -309,7 +309,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Chart - natural gas apparent 1'!B1</f>
+              <f>'Chart - gas consumption y-y'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -330,12 +330,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - natural gas apparent 1'!$A$2:$A$35</f>
+              <f>'Chart - gas consumption y-y'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - natural gas apparent 1'!$B$2:$B$35</f>
+              <f>'Chart - gas consumption y-y'!$B$2:$B$35</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>natural gas apparent consumption</t>
+          <t>gas apparent consumption</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>natural gas apparent consumption y/y</t>
+          <t>gas consumption y/y</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/output/Data and Chart Outputs/china_ndrc_gas_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_ndrc_gas_monthly.xlsx
@@ -158,7 +158,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>China gas apparent consumption (NDRC) (to Jul/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>China gas apparent consumption (NDRC) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -194,12 +195,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$35</f>
+              <f>'Chart'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$35</f>
+              <f>'Chart'!$B$2:$B$36</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -294,7 +295,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>China gas consumption y/y (NDRC) (to Jul/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>China gas consumption y/y (NDRC) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -330,12 +332,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - gas consumption y-y'!$A$2:$A$35</f>
+              <f>'Chart - gas consumption y-y'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - gas consumption y-y'!$B$2:$B$35</f>
+              <f>'Chart - gas consumption y-y'!$B$2:$B$36</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -829,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1117,6 +1119,14 @@
       </c>
       <c r="B35" t="n">
         <v>35.34</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B36" t="n">
+        <v>34.86</v>
       </c>
     </row>
   </sheetData>
@@ -1131,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1419,6 +1429,14 @@
       </c>
       <c r="B35" t="n">
         <v>-2.6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B36" t="n">
+        <v>-4.3</v>
       </c>
     </row>
   </sheetData>
@@ -1433,7 +1451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2039,6 +2057,23 @@
       </c>
       <c r="E35" t="n">
         <v>-2.4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B36" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>277.06</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-2.7</v>
       </c>
     </row>
   </sheetData>
